--- a/problem/C++问题解决逻辑.xlsx
+++ b/problem/C++问题解决逻辑.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yunxiang.xing\Desktop\LBM\fvm_solver\problem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D97B86ED-761D-48BC-A5B5-4CCAE7C632F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C6D5DD6-462B-43BB-935F-81BF03AA4890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="184">
   <si>
     <t>const关键字的作用</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -569,219 +569,195 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>内存分配和释放速度快</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>：栈的内存分配是由操作系统直接管理的，通常以先进后出</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>生命周期短</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>：栈中的变量在函数调用时分配，函数调用结束时自动释放。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>存储数据类型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">：栈通常用于存储基本数据类型（如 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t>int</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t>char</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t>float</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 等）和对象的局部实例（在函数内部声明的对象）。</t>
-    </r>
-  </si>
-  <si>
     <t>堆是用于动态分配内存的区域，由程序员控制分配和释放</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>内存分配和释放速度较慢</t>
-  </si>
-  <si>
-    <r>
-      <t>生命周期长</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>：堆内存的生命周期由程序员控制，直到手动释放</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>存储数据类型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">：堆通常用于存储动态分配的对象（如通过 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t>new</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 或 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-        <family val="2"/>
-      </rPr>
-      <t>malloc</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 创建的对象）和数组</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>内存泄漏</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>：在堆内存中分配了内存但没有正确释放</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>野指针</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>：使用了已释放的堆内存</t>
-    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>内存分配和释放速度快：栈的内存分配是由操作系统直接管理的，通常以先进后出</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命周期短：栈中的变量在函数调用时分配，函数调用结束时自动释放。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存储数据类型：栈通常用于存储基本数据类型（如 int, char, float 等）和对象的局部实例（在函数内部声明的对象）。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命周期长：堆内存的生命周期由程序员控制，直到手动释放</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存储数据类型：堆通常用于存储动态分配的对象（如通过 new 或 malloc 创建的对象）和数组</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>内存泄漏：在堆内存中分配了内存但没有正确释放</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>野指针：使用了已释放的堆内存</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>堆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C++11新特性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>auto</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动类型推断</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遍历容器（如数组、vector、map）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>范围 for 循环</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>std::unique_ptr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>独占，即一个指针指向一块内存，自动释放</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>移动语义，即支持unique_ptr&lt;T&gt;p=move(ptr1);</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>引用计数，允许多个指针指向一个地址，当引用计数为零，释放内存</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>std::shared_ptr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>智能指针</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>支持拷贝，shared_ptr&lt;T&gt;p=ptr1;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>见前文</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用于推导表达式的类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>右值引用和移动语义</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nullptr</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>初始化列表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>强类型枚举类</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>排序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>快速排序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冒泡排序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>插入排序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查找插入</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>map: O(logn);unordered_map: O(1)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>应用场景</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>map：关注元素顺序；unordered_map：只关注查找速度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>点与三角形关系判断</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>海伦公式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>分别构造三个三角形，面积之和为总三角形，则在内部</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>叉积</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>分别判断三条边与点到三角形点向量的叉积，全同号则在内部</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>射线与三角面关系</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>克莱姆法则</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>快速计算交点，满足u、v&gt;=0且u+v&lt;=1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nlonn，logn，递归</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n-n2,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -802,21 +778,6 @@
       <name val="黑体"/>
       <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial Unicode MS"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -845,11 +806,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -860,9 +818,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -871,7 +826,12 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1152,721 +1112,921 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I82"/>
-  <sheetFormatPr defaultRowHeight="17.5"/>
+  <dimension ref="A1:I104"/>
+  <sheetFormatPr defaultRowHeight="17.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="40.9140625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="69.75" style="4" customWidth="1"/>
-    <col min="4" max="7" width="8.6640625" style="2"/>
-    <col min="8" max="9" width="8.6640625" style="3"/>
+    <col min="1" max="1" width="40.9140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="69.75" style="3" customWidth="1"/>
+    <col min="4" max="7" width="8.6640625" style="1"/>
+    <col min="8" max="9" width="8.6640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="7"/>
+      <c r="B2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="4" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="7"/>
+      <c r="B4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="4" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1"/>
-      <c r="B6" s="2" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="7"/>
+      <c r="B6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="4" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="4" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="4" t="s">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1" t="s">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="4" t="s">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="1" t="s">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="8" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="1"/>
-      <c r="B16" s="2" t="s">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="7"/>
+      <c r="B16" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="1"/>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="1"/>
-      <c r="B17" s="2" t="s">
+      <c r="C16" s="7"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="7"/>
+      <c r="B17" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="1"/>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="1" t="s">
+      <c r="C17" s="7"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="1"/>
-      <c r="B19" s="2" t="s">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="7"/>
+      <c r="B19" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="1"/>
-      <c r="B20" s="2" t="s">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="7"/>
+      <c r="B20" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="1"/>
-      <c r="B21" s="2" t="s">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="7"/>
+      <c r="B21" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="3" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="1"/>
-      <c r="B22" s="2" t="s">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="7"/>
+      <c r="B22" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="3" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="1" t="s">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="4" t="s">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1" t="s">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="7"/>
+      <c r="B25" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="4" t="s">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="1" t="s">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="3" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="52.5">
-      <c r="A28" s="1"/>
-      <c r="B28" s="2" t="s">
+    <row r="28" spans="1:3" ht="52.5" x14ac:dyDescent="0.3">
+      <c r="A28" s="7"/>
+      <c r="B28" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="1"/>
-      <c r="B29" s="1" t="s">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="7"/>
+      <c r="B29" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
+    <row r="30" spans="1:3" ht="35" x14ac:dyDescent="0.3">
+      <c r="A30" s="7"/>
+      <c r="B30" s="7"/>
       <c r="C30" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="4" t="s">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="52.5">
-      <c r="A32" s="2" t="s">
+    <row r="32" spans="1:3" ht="52.5" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C32" s="4" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="30.5" customHeight="1">
-      <c r="A33" s="2" t="s">
+    <row r="33" spans="1:3" ht="30.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" s="3" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="1" t="s">
+    <row r="34" spans="1:3" ht="35" x14ac:dyDescent="0.3">
+      <c r="A34" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="1" t="s">
         <v>58</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1" t="s">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="7"/>
+      <c r="B35" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C35" s="3" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="1"/>
-      <c r="B36" s="1"/>
+    <row r="36" spans="1:3" ht="35" x14ac:dyDescent="0.3">
+      <c r="A36" s="7"/>
+      <c r="B36" s="7"/>
       <c r="C36" s="4" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="1"/>
-      <c r="B37" s="1"/>
-      <c r="C37" s="4" t="s">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="7"/>
+      <c r="B37" s="7"/>
+      <c r="C37" s="3" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="1"/>
-      <c r="B38" s="1" t="s">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="7"/>
+      <c r="B38" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" s="3" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="1"/>
-      <c r="B39" s="1"/>
-      <c r="C39" s="4" t="s">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="7"/>
+      <c r="B39" s="7"/>
+      <c r="C39" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="70">
-      <c r="A40" s="1"/>
-      <c r="B40" s="2" t="s">
+    <row r="40" spans="1:3" ht="70" x14ac:dyDescent="0.3">
+      <c r="A40" s="7"/>
+      <c r="B40" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="C40" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="35">
-      <c r="A41" s="1" t="s">
+    <row r="41" spans="1:3" ht="35" x14ac:dyDescent="0.3">
+      <c r="A41" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="C41" s="4" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="1"/>
-      <c r="B42" s="1"/>
-      <c r="C42" s="6" t="s">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="7"/>
+      <c r="B42" s="7"/>
+      <c r="C42" s="4" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="1"/>
-      <c r="B43" s="1" t="s">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="7"/>
+      <c r="B43" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C43" s="6" t="s">
+      <c r="C43" s="4" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
-      <c r="C44" s="6" t="s">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="7"/>
+      <c r="B44" s="7"/>
+      <c r="C44" s="4" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="1" t="s">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C45" s="6" t="s">
+      <c r="C45" s="4" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="1"/>
-      <c r="B46" s="2" t="s">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="7"/>
+      <c r="B46" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C46" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="1"/>
-      <c r="B47" s="2" t="s">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="7"/>
+      <c r="B47" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="C47" s="3" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="1"/>
-      <c r="B48" s="2" t="s">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="7"/>
+      <c r="B48" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C48" s="3" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="1" t="s">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B49" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C49" s="4" t="s">
+      <c r="C49" s="3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="1"/>
-      <c r="B50" s="2" t="s">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="7"/>
+      <c r="B50" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C50" s="4" t="s">
+      <c r="C50" s="3" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="1" t="s">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" s="7"/>
+      <c r="B51" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="7"/>
+      <c r="B52" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B53" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C51" s="4" t="s">
+      <c r="C53" s="3" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="1"/>
-      <c r="B52" s="2" t="s">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="7"/>
+      <c r="B54" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C52" s="4" t="s">
+      <c r="C54" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="2" t="s">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" s="1" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="35" customHeight="1">
-      <c r="A55" s="5" t="s">
+    <row r="57" spans="1:3" ht="35" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="B57" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C55" s="4" t="s">
+      <c r="C57" s="3" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="35">
-      <c r="A56" s="5"/>
-      <c r="B56" s="1" t="s">
+    <row r="58" spans="1:3" ht="35" x14ac:dyDescent="0.3">
+      <c r="A58" s="8"/>
+      <c r="B58" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="C56" s="6" t="s">
+      <c r="C58" s="4" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="31" customHeight="1">
-      <c r="A57" s="5"/>
-      <c r="B57" s="1"/>
-      <c r="C57" s="6" t="s">
+    <row r="59" spans="1:3" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="8"/>
+      <c r="B59" s="7"/>
+      <c r="C59" s="4" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="33" customHeight="1">
-      <c r="A58" s="5"/>
-      <c r="B58" s="2" t="s">
+    <row r="60" spans="1:3" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="8"/>
+      <c r="B60" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C58" s="4" t="s">
+      <c r="C60" s="3" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="38.5" customHeight="1">
-      <c r="A59" s="5" t="s">
+    <row r="61" spans="1:3" ht="38.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="B61" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C59" s="4" t="s">
+      <c r="C61" s="3" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="5"/>
-      <c r="B60" s="1" t="s">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" s="8"/>
+      <c r="B62" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="C60" s="4" t="s">
+      <c r="C62" s="3" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
-      <c r="A61" s="5"/>
-      <c r="B61" s="1"/>
-      <c r="C61" s="4" t="s">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" s="8"/>
+      <c r="B63" s="7"/>
+      <c r="C63" s="3" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
-      <c r="A62" s="5"/>
-      <c r="B62" s="1" t="s">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" s="8"/>
+      <c r="B64" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="C62" s="4" t="s">
+      <c r="C64" s="3" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
-      <c r="A63" s="5"/>
-      <c r="B63" s="1"/>
-      <c r="C63" s="4" t="s">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="8"/>
+      <c r="B65" s="7"/>
+      <c r="C65" s="3" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
-      <c r="A64" s="5"/>
-      <c r="B64" s="2" t="s">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" s="8"/>
+      <c r="B66" s="1" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
-      <c r="A65" s="5"/>
-      <c r="B65" s="2" t="s">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" s="8"/>
+      <c r="B67" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C65" s="4" t="s">
+      <c r="C67" s="3" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
-      <c r="A66" s="1" t="s">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="B68" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C66" s="4" t="s">
+      <c r="C68" s="3" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
-      <c r="A67" s="1"/>
-      <c r="B67" s="2" t="s">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" s="7"/>
+      <c r="B69" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C67" s="4" t="s">
+      <c r="C69" s="3" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
-      <c r="A68" s="5" t="s">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="B70" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="40" customHeight="1">
-      <c r="A69" s="5"/>
-      <c r="B69" s="2" t="s">
+    <row r="71" spans="1:3" ht="40" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="8"/>
+      <c r="B71" s="1" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
-      <c r="A70" s="1" t="s">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="B72" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C70" s="4" t="s">
+      <c r="C72" s="3" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
-      <c r="A71" s="1"/>
-      <c r="B71" s="2" t="s">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" s="7"/>
+      <c r="B73" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C71" s="4" t="s">
+      <c r="C73" s="3" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
-      <c r="A72" s="7" t="s">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="B72" s="7" t="s">
+      <c r="B74" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="C72" s="8" t="s">
+      <c r="C74" s="6" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
-      <c r="A73" s="2" t="s">
+    <row r="75" spans="1:3" ht="35" x14ac:dyDescent="0.3">
+      <c r="A75" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="B75" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C75" s="4" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
-      <c r="C74" s="9" t="s">
+    <row r="76" spans="1:3" ht="35" x14ac:dyDescent="0.3">
+      <c r="A76" s="7"/>
+      <c r="B76" s="7"/>
+      <c r="C76" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" ht="35" x14ac:dyDescent="0.3">
+      <c r="A77" s="7"/>
+      <c r="B77" s="7"/>
+      <c r="C77" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="35" x14ac:dyDescent="0.3">
+      <c r="A78" s="7"/>
+      <c r="B78" s="7"/>
+      <c r="C78" s="4" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" s="7"/>
+      <c r="B79" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="C79" s="4" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
-      <c r="C75" s="9" t="s">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" s="7"/>
+      <c r="B80" s="7"/>
+      <c r="C80" s="4" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
-      <c r="C76" s="9" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3">
-      <c r="C77" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3">
-      <c r="C78" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3">
-      <c r="C79" s="9" t="s">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81" s="7"/>
+      <c r="B81" s="7"/>
+      <c r="C81" s="4" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
-      <c r="C80" s="9" t="s">
+    <row r="82" spans="1:3" ht="35" x14ac:dyDescent="0.3">
+      <c r="A82" s="7"/>
+      <c r="B82" s="7"/>
+      <c r="C82" s="4" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="81" spans="3:3">
-      <c r="C81" s="9" t="s">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83" s="7"/>
+      <c r="B83" s="7"/>
+      <c r="C83" s="4" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="82" spans="3:3">
-      <c r="C82" s="9" t="s">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84" s="7"/>
+      <c r="B84" s="7"/>
+      <c r="C84" s="4" t="s">
         <v>146</v>
       </c>
     </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86" s="7"/>
+      <c r="B86" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87" s="7"/>
+      <c r="B87" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88" s="7"/>
+      <c r="B88" s="7"/>
+      <c r="C88" s="4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89" s="7"/>
+      <c r="B89" s="7"/>
+      <c r="C89" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A90" s="7"/>
+      <c r="B90" s="7"/>
+      <c r="C90" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" ht="35" x14ac:dyDescent="0.3">
+      <c r="A91" s="7"/>
+      <c r="B91" s="7"/>
+      <c r="C91" s="4" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A92" s="7"/>
+      <c r="B92" s="7"/>
+      <c r="C92" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A93" s="7"/>
+      <c r="B93" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A94" s="7"/>
+      <c r="B94" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95" s="7"/>
+      <c r="B95" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A96" s="7"/>
+      <c r="B96" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" s="7"/>
+      <c r="B97" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98" s="7"/>
+      <c r="B98" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100" s="7"/>
+      <c r="B100" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A102" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A103" s="7"/>
+      <c r="B103" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A104" s="7"/>
+      <c r="B104" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>183</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="33">
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="A59:A65"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="A70:A71"/>
-    <mergeCell ref="A45:A48"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="A55:A58"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="A34:A40"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="A41:A44"/>
-    <mergeCell ref="A18:A22"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="A23:A26"/>
-    <mergeCell ref="B29:B31"/>
-    <mergeCell ref="A27:A31"/>
-    <mergeCell ref="B35:B37"/>
+  <mergeCells count="40">
+    <mergeCell ref="A102:A104"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B75:B78"/>
+    <mergeCell ref="B79:B84"/>
+    <mergeCell ref="A75:A84"/>
+    <mergeCell ref="B87:B92"/>
+    <mergeCell ref="A85:A98"/>
     <mergeCell ref="B13:B14"/>
     <mergeCell ref="A7:A14"/>
     <mergeCell ref="A15:A17"/>
@@ -1877,6 +2037,29 @@
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="B11:B12"/>
+    <mergeCell ref="A18:A22"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="A23:A26"/>
+    <mergeCell ref="B29:B31"/>
+    <mergeCell ref="A27:A31"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="A34:A40"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="A41:A44"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="A45:A48"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="A57:A60"/>
+    <mergeCell ref="A49:A52"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="A61:A67"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="B62:B63"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
